--- a/artfynd/A 37421-2022 artfynd.xlsx
+++ b/artfynd/A 37421-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37421-2022 artfynd.xlsx
+++ b/artfynd/A 37421-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6081703</v>
+        <v>236437</v>
       </c>
       <c r="B2" t="n">
-        <v>103399</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,22 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224190</v>
+        <v>167</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flockarun</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Centaurium erythraea var. erythraea</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Botrychium multifidum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(S. G. Gmel.) Rupr.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -716,17 +715,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lugnet, V om, Öl</t>
+          <t>Böda kyrka 1,5 km norr, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623732.5335790801</v>
+        <v>623804</v>
       </c>
       <c r="R2" t="n">
-        <v>6348369.337465874</v>
+        <v>6348473</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,34 +747,14 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Hö-Bor-0231</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-08-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Höstlåsbräken, kruståtel, gulmåra, ljung, sandstarr, ängssyra, tall.</t>
+          <t>2009-08-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,37 +768,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Torr-frisk dynveg.</t>
+          <t>sandstrand med dyner</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Öland- Floraväktarna</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Lennart Johnsson, Sakari Öistämö, Ingrid Johnsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>236439</v>
+        <v>236438</v>
       </c>
       <c r="B3" t="n">
-        <v>95596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,20 +818,29 @@
           <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Böda Kyrketorp N, Öl</t>
+          <t>Böda kyrka 1,5 km norr, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623807.9920522165</v>
+        <v>623810</v>
       </c>
       <c r="R3" t="n">
-        <v>6348420.315269426</v>
+        <v>6348425</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-08-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,33 +883,32 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sandstrand</t>
+          <t>sandstrand med dyner</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Lennart Johnsson, Ingrid Johnsson, Sakari Öistämö, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>236437</v>
+        <v>236439</v>
       </c>
       <c r="B4" t="n">
-        <v>95596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,29 +933,20 @@
           <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Böda kyrka 1,5 km norr, Öl</t>
+          <t>Böda Kyrketorp N, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623804.2278127143</v>
+        <v>623808</v>
       </c>
       <c r="R4" t="n">
-        <v>6348473.233934105</v>
+        <v>6348420</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-08-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-08-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,33 +989,32 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>sandstrand med dyner</t>
+          <t>Sandstrand</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Lennart Johnsson, Sakari Öistämö, Ingrid Johnsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>236438</v>
+        <v>236449</v>
       </c>
       <c r="B5" t="n">
-        <v>95596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1041,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,17 +1051,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Böda kyrka 1,5 km norr, Öl</t>
+          <t>NO Bödagården, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623810.0122395083</v>
+        <v>623810</v>
       </c>
       <c r="R5" t="n">
-        <v>6348425.246503033</v>
+        <v>6348426</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2009-08-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2009-08-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,36 +1101,30 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>sandstrand med dyner</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Lennart Johnsson, Ingrid Johnsson, Sakari Öistämö, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>236449</v>
+        <v>237484</v>
       </c>
       <c r="B6" t="n">
-        <v>95596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1151,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1225,17 +1161,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NO Bödagården, Öl</t>
+          <t>Böda ost, Ölandsgården ost, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623809.9796392681</v>
+        <v>623811</v>
       </c>
       <c r="R6" t="n">
-        <v>6348426.327814505</v>
+        <v>6348424</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,22 +1195,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2009-09-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2009-09-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,31 +1211,35 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sanddyner</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>237484</v>
+        <v>239940</v>
       </c>
       <c r="B7" t="n">
-        <v>95596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1266,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1346,14 +1276,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Böda ost, Ölandsgården ost, Öl</t>
+          <t>Bödagården NO, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623811.1282829639</v>
+        <v>623810</v>
       </c>
       <c r="R7" t="n">
-        <v>6348424.197855925</v>
+        <v>6348421</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1380,22 +1310,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-08-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-08-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,33 +1329,32 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>sanddyner</t>
+          <t>igenväxande sanddyner</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Jan-Olof Petersson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Mikael Gemsjö</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>231338</v>
+        <v>6903795</v>
       </c>
       <c r="B8" t="n">
-        <v>95596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,22 +1381,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnet, Böda, Borgholm, Öl</t>
+          <t>Bödagården NO, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623757.925599219</v>
+        <v>623813</v>
       </c>
       <c r="R8" t="n">
-        <v>6348354.409095026</v>
+        <v>6348419</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1501,27 +1425,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1990-09-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1990-09-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Avlång förekomst, finns utmed en ca. 700 m lång sträcka parallellt med strandlinjen</t>
+          <t>varav 2 med sporax</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,36 +1447,29 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gräsbevuxen dynsvacka</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helena Lager</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Helena Lager</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Jan-Olof Petersson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>239940</v>
+        <v>7027933</v>
       </c>
       <c r="B9" t="n">
-        <v>95597</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1496,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1597,19 +1504,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bödagården NO, Öl</t>
+          <t>Bödagården, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623810.142640519</v>
+        <v>623805</v>
       </c>
       <c r="R9" t="n">
-        <v>6348420.921254308</v>
+        <v>6348432</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1633,22 +1542,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2012-08-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2012-08-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,74 +1558,79 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>igenväxande sanddyner</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Henrik Wegnelius</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Mikael Gemsiö</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Henrik Wegnelius</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6903796</v>
+        <v>7027934</v>
       </c>
       <c r="B10" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>167</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(S. G. Gmel.) Rupr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bödagården NO, Öl</t>
+          <t>Bödagården, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623812.9001521464</v>
+        <v>623808</v>
       </c>
       <c r="R10" t="n">
-        <v>6348419.380947076</v>
+        <v>6348424</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1750,22 +1654,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2013-08-16</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-08-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 ex. med sporax</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,27 +1679,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Henrik Wegnelius</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Jan-Olof Petersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Henrik Wegnelius</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6903795</v>
+        <v>16542177</v>
       </c>
       <c r="B11" t="n">
-        <v>95597</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,7 +1725,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1835,16 +1733,18 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bödagården NO, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623812.9001521464</v>
+        <v>623812</v>
       </c>
       <c r="R11" t="n">
-        <v>6348419.380947076</v>
+        <v>6348423</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1871,27 +1771,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2013-08-16</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-08-16</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>varav 2 med sporax</t>
+          <t>med sporax, minimala i storlek</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,6 +1792,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>igenväxande dynsvackor på sand</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1914,46 +1809,41 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson, Jan-Olof Petersson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7027933</v>
+        <v>6081703</v>
       </c>
       <c r="B12" t="n">
-        <v>95597</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>167</v>
+        <v>224190</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Flockarun</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(S. G. Gmel.) Rupr.</t>
-        </is>
-      </c>
+          <t>Centaurium erythraea var. erythraea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1961,21 +1851,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bödagården, Öl</t>
+          <t>Lugnet, V om, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623804.9248531591</v>
+        <v>623733</v>
       </c>
       <c r="R12" t="n">
-        <v>6348432.128035327</v>
+        <v>6348369</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1997,24 +1885,24 @@
           <t>Böda</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Hö-Bor-0231</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2013-08-30</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-08-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2013-08-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-08-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken, kruståtel, gulmåra, ljung, sandstarr, ängssyra, tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,31 +1913,35 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Torr-frisk dynveg.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Henrik Wegnelius</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Henrik Wegnelius</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7027934</v>
+        <v>68792021</v>
       </c>
       <c r="B13" t="n">
-        <v>95597</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>3739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,48 +1949,51 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>167</v>
+        <v>101049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Sammetsfrölöpare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Harpalus griseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
+          <t>(Panzer, 1797)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bödagården, Öl</t>
+          <t>Böda baden, utmed stranden upp till Svartvikskärrets utlopp., Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623807.877953317</v>
+        <v>623782</v>
       </c>
       <c r="R13" t="n">
-        <v>6348424.099862842</v>
+        <v>6348420</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2122,27 +2017,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2013-08-30</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-07-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2013-08-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-07-20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2 ex. med sporax</t>
+          <t>nattfångst på sandstrand.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2153,80 +2038,94 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Sandstrand med dyner, strandråg.</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>2247</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Henrik Wegnelius</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Henrik Wegnelius</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16542177</v>
+        <v>65791448</v>
       </c>
       <c r="B14" t="n">
-        <v>95597</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>167</v>
+        <v>102625</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bödagården NO, Öl</t>
+          <t>Fagerumsstrandmyr, Svartvikskärret, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623812.2443269903</v>
+        <v>623603</v>
       </c>
       <c r="R14" t="n">
-        <v>6348423.149208829</v>
+        <v>6348513</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2250,27 +2149,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>med sporax, minimala i storlek</t>
+          <t>2017-05-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2281,36 +2165,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>igenväxande dynsvackor på sand</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Lina Tomasson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Jan-Olof Petersson</t>
+          <t>Lina Tomasson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16542176</v>
+        <v>109642631</v>
       </c>
       <c r="B15" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2318,37 +2192,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>208245</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bödagården NO, Öl</t>
+          <t>Bödagården, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623812.2117261693</v>
+        <v>623719</v>
       </c>
       <c r="R15" t="n">
-        <v>6348424.230520858</v>
+        <v>6348266</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2375,22 +2251,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2399,13 +2265,9 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>igenväxande svacka i sanddyner</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2415,22 +2277,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Jan-Olof Petersson</t>
+          <t>Ulla-Britt Andersson, Jan-Olof Petersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66975036</v>
+        <v>15953049</v>
       </c>
       <c r="B16" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2438,41 +2295,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>219677</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bödagården norrut, Öl</t>
+          <t>Svartvikskärret ost, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623779.9894104534</v>
+        <v>623641</v>
       </c>
       <c r="R16" t="n">
-        <v>6348431.917512759</v>
+        <v>6348528</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2499,22 +2352,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,11 +2368,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>fuktig tallskog innanför sanddyner</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2539,22 +2377,21 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Bengt Westman, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66975033</v>
+        <v>109642587</v>
       </c>
       <c r="B17" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2562,37 +2399,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bödagården norrut, Öl</t>
+          <t>Bödagården, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623779.9894104534</v>
+        <v>623672</v>
       </c>
       <c r="R17" t="n">
-        <v>6348431.917512759</v>
+        <v>6348495</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2619,22 +2457,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2643,13 +2471,9 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>fuktig tallskog innanför sanddyner</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2659,22 +2483,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson, Jan-Olof Petersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66974960</v>
+        <v>109642540</v>
       </c>
       <c r="B18" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99010</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,37 +2501,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>219769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bödagården norrut, Öl</t>
+          <t>Bödagården, Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623785.3531819129</v>
+        <v>623772</v>
       </c>
       <c r="R18" t="n">
-        <v>6348487.816861708</v>
+        <v>6348450</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2739,22 +2559,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2763,13 +2573,9 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>fuktig tallskog innanför sanddyner</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2779,22 +2585,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson, Jan-Olof Petersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66975014</v>
+        <v>66975036</v>
       </c>
       <c r="B19" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,26 +2603,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2829,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623775.7124573831</v>
+        <v>623780</v>
       </c>
       <c r="R19" t="n">
-        <v>6348465.880661599</v>
+        <v>6348432</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2862,19 +2667,9 @@
           <t>2017-08-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2902,71 +2697,64 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>68792021</v>
+        <v>103708876</v>
       </c>
       <c r="B20" t="n">
-        <v>3679</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101049</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sammetsfrölöpare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Harpalus griseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Panzer, 1797)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Böda baden, utmed stranden upp till Svartvikskärrets utlopp., Öl</t>
+          <t>Bödagården norrut, Öl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623781.9893894279</v>
+        <v>623755</v>
       </c>
       <c r="R20" t="n">
-        <v>6348419.531416991</v>
+        <v>6348498</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2990,27 +2778,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2002-07-20</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2002-07-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>nattfångst på sandstrand.</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3019,48 +2792,34 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Sandstrand med dyner, strandråg.</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>Håkan Lundkvist</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>2247</t>
+          <t>alsumpskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102218349</v>
+        <v>66975033</v>
       </c>
       <c r="B21" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3068,43 +2827,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO om lugnet, Öl</t>
+          <t>Bödagården norrut, Öl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623796.313964624</v>
+        <v>623780</v>
       </c>
       <c r="R21" t="n">
-        <v>6348465.960518876</v>
+        <v>6348432</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3128,22 +2884,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,31 +2900,35 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>fuktig tallskog innanför sanddyner</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103708876</v>
+        <v>103708900</v>
       </c>
       <c r="B22" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3186,30 +2936,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3218,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623755.2168018945</v>
+        <v>623764</v>
       </c>
       <c r="R22" t="n">
-        <v>6348498.272453973</v>
+        <v>6348434</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3251,19 +2997,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3278,7 +3014,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>alsumpskog</t>
+          <t>alsumpskog med björk</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3296,15 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103708867</v>
+        <v>66841560</v>
       </c>
       <c r="B23" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3312,41 +3043,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>219799</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bödagården norrut, Öl</t>
+          <t>Fagerumsstrandmyr, Svartvikskärret, Öl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623755.2168018945</v>
+        <v>623603</v>
       </c>
       <c r="R23" t="n">
-        <v>6348498.272453973</v>
+        <v>6348513</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3370,22 +3104,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3394,39 +3118,32 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>alsumpskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Lina Tomasson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Lina Tomasson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103708906</v>
+        <v>109642548</v>
       </c>
       <c r="B24" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3434,21 +3151,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221725</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3458,14 +3175,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bödagården norrut, Öl</t>
+          <t>Bödagården, Öl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623773.0408358302</v>
+        <v>623772</v>
       </c>
       <c r="R24" t="n">
-        <v>6348410.603328492</v>
+        <v>6348450</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3492,22 +3209,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3520,11 +3227,6 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>igenväxande, fuktiga dynsvackor</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
@@ -3533,22 +3235,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+          <t>Ulla-Britt Andersson, Jan-Olof Petersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103708688</v>
+        <v>2872979</v>
       </c>
       <c r="B25" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3556,38 +3253,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bödagården norrut, Öl</t>
+          <t>Lugnet, Öl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623798.8968666145</v>
+        <v>623603</v>
       </c>
       <c r="R25" t="n">
-        <v>6348416.253039141</v>
+        <v>6348519</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3614,22 +3307,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3638,81 +3321,77 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>igenväxande dyner med tall</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Patrik Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Patrik Engström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103708900</v>
+        <v>65792492</v>
       </c>
       <c r="B26" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106139</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bödagården norrut, Öl</t>
+          <t>Fagerumsstrandmyr, Svartvikskärret, Öl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623763.67261771</v>
+        <v>623603</v>
       </c>
       <c r="R26" t="n">
-        <v>6348433.59031506</v>
+        <v>6348513</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3736,22 +3415,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3760,39 +3429,32 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>alsumpskog med björk</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Lina Tomasson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Lina Tomasson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109642587</v>
+        <v>6903796</v>
       </c>
       <c r="B27" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106228</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3800,38 +3462,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219677</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bödagården, Öl</t>
+          <t>Bödagården NO, Öl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623672.367455219</v>
+        <v>623813</v>
       </c>
       <c r="R27" t="n">
-        <v>6348494.694251488</v>
+        <v>6348419</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3858,22 +3516,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3882,7 +3530,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3894,22 +3541,21 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Jan-Olof Petersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Jan-Olof Petersson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109642538</v>
+        <v>15953048</v>
       </c>
       <c r="B28" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106228</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3936,23 +3582,18 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bödagården, Öl</t>
+          <t>Svartvikskärret ost, Öl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623772.4093007762</v>
+        <v>623641</v>
       </c>
       <c r="R28" t="n">
-        <v>6348449.54682397</v>
+        <v>6348528</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3979,22 +3620,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4003,7 +3634,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4015,22 +3645,21 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Jan-Olof Petersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Bengt Westman, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109642548</v>
+        <v>16542176</v>
       </c>
       <c r="B29" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4038,38 +3667,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bödagården, Öl</t>
+          <t>Bödagården NO, Öl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623772.4093007762</v>
+        <v>623812</v>
       </c>
       <c r="R29" t="n">
-        <v>6348449.54682397</v>
+        <v>6348424</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4096,22 +3724,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4120,9 +3738,13 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>igenväxande svacka i sanddyner</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4132,22 +3754,21 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Jan-Olof Petersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109642540</v>
+        <v>66974960</v>
       </c>
       <c r="B30" t="n">
-        <v>96225</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,38 +3776,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219769</v>
+        <v>221725</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bödagården, Öl</t>
+          <t>Bödagården norrut, Öl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623772.4093007762</v>
+        <v>623785</v>
       </c>
       <c r="R30" t="n">
-        <v>6348449.54682397</v>
+        <v>6348488</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4213,22 +3833,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4237,9 +3847,13 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>fuktig tallskog innanför sanddyner</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4249,61 +3863,59 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Jan-Olof Petersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111885493</v>
+        <v>66975014</v>
       </c>
       <c r="B31" t="n">
-        <v>95785</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>167</v>
+        <v>221725</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bödagården NO, Öl</t>
+          <t>Bödagården norrut, Öl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>623796</v>
+        <v>623776</v>
       </c>
       <c r="R31" t="n">
-        <v>6348424</v>
+        <v>6348466</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4330,27 +3942,26 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="AD31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>nyröjt område mellan sanddyner</t>
+          <t>fuktig tallskog innanför sanddyner</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4364,7 +3975,745 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>102218349</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NO om lugnet, Öl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>623797</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6348466</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>103708688</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bödagården norrut, Öl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>623799</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6348416</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>igenväxande dyner med tall</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>103708867</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bödagården norrut, Öl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>623755</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6348498</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>103708906</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bödagården norrut, Öl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>623773</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6348411</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>igenväxande, fuktiga dynsvackor</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>109642538</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bödagården, Öl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>623772</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6348450</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Jan-Olof Petersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>66841606</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99878</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fagerumsstrandmyr, Svartvikskärret, Öl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>623603</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6348513</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2017-07-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2017-07-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Lina Tomasson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Lina Tomasson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>15953007</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svartvikskärret ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>623626</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6348526</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2014-06-05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2014-06-05</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Bengt Westman, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37421-2022 artfynd.xlsx
+++ b/artfynd/A 37421-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/236437</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/236438</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/236439</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/236449</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/237484</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/239940</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6903795</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1575,6 +1615,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7027933</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1692,6 +1737,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7027934</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1814,6 +1864,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16542177</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1935,6 +1990,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6081703</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2066,6 +2126,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68792021</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2178,6 +2243,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65791448</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2281,6 +2351,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109642631</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2383,6 +2458,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15953049</t>
         </is>
       </c>
     </row>
@@ -2487,6 +2567,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109642587</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2589,6 +2674,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109642540</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2702,6 +2792,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66975036</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2813,6 +2908,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103708876</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2920,6 +3020,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66975033</t>
         </is>
       </c>
     </row>
@@ -3029,6 +3134,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103708900</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3245,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66841560</t>
         </is>
       </c>
     </row>
@@ -3239,6 +3354,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109642548</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3340,6 +3460,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2872979</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3448,6 +3573,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65792492</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3547,6 +3677,11 @@
       <c r="AY27" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6903796</t>
         </is>
       </c>
     </row>
@@ -3653,6 +3788,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15953048</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3762,6 +3902,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16542176</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3871,6 +4016,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66974960</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3980,6 +4130,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66975014</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4083,6 +4238,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102218349</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4190,6 +4350,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103708688</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4297,6 +4462,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103708867</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4404,6 +4574,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103708906</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4510,6 +4685,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109642538</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4612,6 +4792,11 @@
       <c r="AY37" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66841606</t>
         </is>
       </c>
     </row>
@@ -4714,8 +4899,52 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15953007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>